--- a/base1.xlsx
+++ b/base1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0000\Documentos\GitHub\Lavaseca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0000\Documentos\GitHub\Lavas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA35A8-BBFA-49FE-AD53-C9127AD25910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412F4000-3E63-4432-BA4D-BDB7AC7F254B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{46D2FD60-5EF8-4D26-8876-8A275CECFA74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
   <si>
     <t>activo</t>
   </si>
@@ -1022,25 +1022,40 @@
       <c r="A53">
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
+      <c r="B54" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">

--- a/base1.xlsx
+++ b/base1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0000\Documentos\GitHub\Lavas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412F4000-3E63-4432-BA4D-BDB7AC7F254B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73109C69-F470-4F66-B26B-6A3946F7648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{46D2FD60-5EF8-4D26-8876-8A275CECFA74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
   <si>
     <t>activo</t>
   </si>
@@ -1062,30 +1062,48 @@
       <c r="A58">
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
+      <c r="B60" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">

--- a/base1.xlsx
+++ b/base1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0000\Documentos\GitHub\Lavas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73109C69-F470-4F66-B26B-6A3946F7648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2209EC00-0F25-422B-9D2C-D2B11721FD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{46D2FD60-5EF8-4D26-8876-8A275CECFA74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
   <si>
     <t>activo</t>
   </si>
@@ -1110,6 +1110,9 @@
       <c r="A64">
         <v>62</v>
       </c>
+      <c r="B64" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65">

--- a/base1.xlsx
+++ b/base1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0000\Documentos\GitHub\Lavas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2209EC00-0F25-422B-9D2C-D2B11721FD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61C8D16-4C9C-4158-9379-990F4105A188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{46D2FD60-5EF8-4D26-8876-8A275CECFA74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="27">
   <si>
     <t>activo</t>
   </si>
@@ -1114,82 +1114,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
